--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/63.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/63.xlsx
@@ -426,13 +426,13 @@
         <v>-12.24838645723191</v>
       </c>
       <c r="E2">
-        <v>-6.663945929805031</v>
+        <v>-9.019178090350339</v>
       </c>
       <c r="F2">
-        <v>-3.099940664658499</v>
+        <v>-3.494353721255636</v>
       </c>
       <c r="G2">
-        <v>-11.16209140288159</v>
+        <v>-14.04185220385512</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.60375081065026</v>
       </c>
       <c r="E3">
-        <v>-5.906576765918195</v>
+        <v>-9.013019365699908</v>
       </c>
       <c r="F3">
-        <v>-2.438913417633327</v>
+        <v>-3.446040020854757</v>
       </c>
       <c r="G3">
-        <v>-9.875623337957427</v>
+        <v>-13.78836373191312</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.93550405308918</v>
       </c>
       <c r="E4">
-        <v>-7.105725740097321</v>
+        <v>-9.31457950681869</v>
       </c>
       <c r="F4">
-        <v>-2.961795489628431</v>
+        <v>-3.429668995873231</v>
       </c>
       <c r="G4">
-        <v>-9.779481784951452</v>
+        <v>-14.23638317028823</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.33537470741062</v>
       </c>
       <c r="E5">
-        <v>-7.312446050073465</v>
+        <v>-9.636744204672375</v>
       </c>
       <c r="F5">
-        <v>-2.852561165323468</v>
+        <v>-3.16446137329515</v>
       </c>
       <c r="G5">
-        <v>-9.864364172578366</v>
+        <v>-13.14702167622673</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.784628034477082</v>
       </c>
       <c r="E6">
-        <v>-7.880121966252998</v>
+        <v>-10.29151173296743</v>
       </c>
       <c r="F6">
-        <v>-2.611641274995469</v>
+        <v>-2.967573352262957</v>
       </c>
       <c r="G6">
-        <v>-9.957993021520034</v>
+        <v>-13.3568241892325</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.31391061646066</v>
       </c>
       <c r="E7">
-        <v>-9.305237264940867</v>
+        <v>-10.96292593171467</v>
       </c>
       <c r="F7">
-        <v>-2.209339675621472</v>
+        <v>-2.97784759315988</v>
       </c>
       <c r="G7">
-        <v>-9.448125971380259</v>
+        <v>-12.05395899225233</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.922494350524946</v>
       </c>
       <c r="E8">
-        <v>-9.854423421747082</v>
+        <v>-12.0692683595806</v>
       </c>
       <c r="F8">
-        <v>-2.071855537778838</v>
+        <v>-3.32751886959701</v>
       </c>
       <c r="G8">
-        <v>-8.309447280420239</v>
+        <v>-13.09769123714605</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.629564329932464</v>
       </c>
       <c r="E9">
-        <v>-10.734052326893</v>
+        <v>-12.09013103933394</v>
       </c>
       <c r="F9">
-        <v>-2.040909388345054</v>
+        <v>-2.809721316720289</v>
       </c>
       <c r="G9">
-        <v>-8.308513706578164</v>
+        <v>-11.60401943746444</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.4366145439745</v>
       </c>
       <c r="E10">
-        <v>-12.66995232280204</v>
+        <v>-12.40529471637176</v>
       </c>
       <c r="F10">
-        <v>-2.403658929337583</v>
+        <v>-3.230784609400292</v>
       </c>
       <c r="G10">
-        <v>-7.511721674549757</v>
+        <v>-11.10369669011439</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.34247887551957</v>
       </c>
       <c r="E11">
-        <v>-12.32401313640809</v>
+        <v>-12.28777628739871</v>
       </c>
       <c r="F11">
-        <v>-2.11323745975309</v>
+        <v>-2.923540654599747</v>
       </c>
       <c r="G11">
-        <v>-7.390370317262232</v>
+        <v>-11.27700374909523</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.344907861853718</v>
       </c>
       <c r="E12">
-        <v>-12.92280419749432</v>
+        <v>-13.21240463875885</v>
       </c>
       <c r="F12">
-        <v>-2.231329516696188</v>
+        <v>-2.973733092270174</v>
       </c>
       <c r="G12">
-        <v>-6.612892007909934</v>
+        <v>-10.61338834302063</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.421751603017446</v>
       </c>
       <c r="E13">
-        <v>-13.40822038332453</v>
+        <v>-14.89926573509007</v>
       </c>
       <c r="F13">
-        <v>-2.511740994585251</v>
+        <v>-2.964341062657234</v>
       </c>
       <c r="G13">
-        <v>-7.478814851889402</v>
+        <v>-9.873296024443318</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.565101196013604</v>
       </c>
       <c r="E14">
-        <v>-13.66202323755842</v>
+        <v>-15.04640491254729</v>
       </c>
       <c r="F14">
-        <v>-2.124870223190603</v>
+        <v>-2.443814039188289</v>
       </c>
       <c r="G14">
-        <v>-5.147614757318652</v>
+        <v>-9.436052411798538</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.740842301244221</v>
       </c>
       <c r="E15">
-        <v>-16.37492333217754</v>
+        <v>-15.70773872815346</v>
       </c>
       <c r="F15">
-        <v>-1.986429320997736</v>
+        <v>-2.040057826654976</v>
       </c>
       <c r="G15">
-        <v>-5.537540742570631</v>
+        <v>-9.493020279438316</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.936137275785974</v>
       </c>
       <c r="E16">
-        <v>-15.21929299321213</v>
+        <v>-17.30587343325239</v>
       </c>
       <c r="F16">
-        <v>-1.388523670065887</v>
+        <v>-2.205659239250834</v>
       </c>
       <c r="G16">
-        <v>-4.820403746762628</v>
+        <v>-9.5934787838275</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.117606715084195</v>
       </c>
       <c r="E17">
-        <v>-16.80811715575129</v>
+        <v>-18.29171769624822</v>
       </c>
       <c r="F17">
-        <v>-1.653589641818089</v>
+        <v>-2.049221226864745</v>
       </c>
       <c r="G17">
-        <v>-5.07303809795549</v>
+        <v>-9.359601983660149</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.275277435864476</v>
       </c>
       <c r="E18">
-        <v>-18.12435435387274</v>
+        <v>-18.52871991191366</v>
       </c>
       <c r="F18">
-        <v>-0.7880028632433991</v>
+        <v>-1.506686138238222</v>
       </c>
       <c r="G18">
-        <v>-4.271154446887684</v>
+        <v>-8.542162079103306</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.382339078690034</v>
       </c>
       <c r="E19">
-        <v>-18.56589868351663</v>
+        <v>-18.46712360846133</v>
       </c>
       <c r="F19">
-        <v>-0.8546342520223829</v>
+        <v>-1.263377236320548</v>
       </c>
       <c r="G19">
-        <v>-4.814150126238944</v>
+        <v>-8.711317713977907</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.4326998249404</v>
       </c>
       <c r="E20">
-        <v>-19.67236338018077</v>
+        <v>-19.61950703156324</v>
       </c>
       <c r="F20">
-        <v>-0.2395200966647764</v>
+        <v>-0.9797053043340662</v>
       </c>
       <c r="G20">
-        <v>-4.638231046827613</v>
+        <v>-9.632347899004083</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.409269603759649</v>
       </c>
       <c r="E21">
-        <v>-19.93824820306713</v>
+        <v>-20.91391245649371</v>
       </c>
       <c r="F21">
-        <v>-0.7683299657943136</v>
+        <v>-0.9291276758213368</v>
       </c>
       <c r="G21">
-        <v>-4.61098856758495</v>
+        <v>-8.166444955305881</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.314133449930026</v>
       </c>
       <c r="E22">
-        <v>-19.92594433918829</v>
+        <v>-20.34409004363454</v>
       </c>
       <c r="F22">
-        <v>-0.196007613730524</v>
+        <v>-0.4468894504445907</v>
       </c>
       <c r="G22">
-        <v>-5.235850727576848</v>
+        <v>-8.833473533831475</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.144934719358663</v>
       </c>
       <c r="E23">
-        <v>-20.65289121469159</v>
+        <v>-21.49968868328191</v>
       </c>
       <c r="F23">
-        <v>-0.0766647220091992</v>
+        <v>-0.3308036993510735</v>
       </c>
       <c r="G23">
-        <v>-4.850993187545494</v>
+        <v>-9.06184158622148</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.908669870391932</v>
       </c>
       <c r="E24">
-        <v>-20.53609281308576</v>
+        <v>-21.11787039732518</v>
       </c>
       <c r="F24">
-        <v>-0.07563257622531101</v>
+        <v>-0.3068539410013342</v>
       </c>
       <c r="G24">
-        <v>-3.745565615981912</v>
+        <v>-8.937520669585229</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.614789428936042</v>
       </c>
       <c r="E25">
-        <v>-21.17258794875986</v>
+        <v>-21.24798251251356</v>
       </c>
       <c r="F25">
-        <v>0.107307394478543</v>
+        <v>-0.393697494408626</v>
       </c>
       <c r="G25">
-        <v>-4.427494959979766</v>
+        <v>-9.016003772684732</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.269521078728093</v>
       </c>
       <c r="E26">
-        <v>-21.4142590211272</v>
+        <v>-21.37255630399057</v>
       </c>
       <c r="F26">
-        <v>0.2521698007779121</v>
+        <v>-0.6226623863794233</v>
       </c>
       <c r="G26">
-        <v>-5.426928795012501</v>
+        <v>-9.50163762947704</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.889731073864555</v>
       </c>
       <c r="E27">
-        <v>-21.63155784638527</v>
+        <v>-21.48320503789398</v>
       </c>
       <c r="F27">
-        <v>0.1306872360551563</v>
+        <v>-0.3509073478496147</v>
       </c>
       <c r="G27">
-        <v>-5.381958344407042</v>
+        <v>-8.922176291010707</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.479539342228947</v>
       </c>
       <c r="E28">
-        <v>-21.86267757431474</v>
+        <v>-20.78072550745412</v>
       </c>
       <c r="F28">
-        <v>-0.5200856508907605</v>
+        <v>-0.1718300543450148</v>
       </c>
       <c r="G28">
-        <v>-5.351961491275706</v>
+        <v>-9.151756003068085</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.058294648399976</v>
       </c>
       <c r="E29">
-        <v>-22.11247272905184</v>
+        <v>-21.15650733755862</v>
       </c>
       <c r="F29">
-        <v>-0.3577952228038926</v>
+        <v>-0.4551549003897241</v>
       </c>
       <c r="G29">
-        <v>-4.954593399651446</v>
+        <v>-9.158946507979381</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.626830660246864</v>
       </c>
       <c r="E30">
-        <v>-21.59185218628601</v>
+        <v>-20.58571583126181</v>
       </c>
       <c r="F30">
-        <v>-0.2991376986442568</v>
+        <v>-0.6127592540789553</v>
       </c>
       <c r="G30">
-        <v>-5.718157486102188</v>
+        <v>-9.126278044597854</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.19926224480287</v>
       </c>
       <c r="E31">
-        <v>-20.53366102254364</v>
+        <v>-20.66601473236582</v>
       </c>
       <c r="F31">
-        <v>-0.1458209746319159</v>
+        <v>-0.6374446026823806</v>
       </c>
       <c r="G31">
-        <v>-4.432384635741269</v>
+        <v>-8.445464354446734</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.772130736576452</v>
       </c>
       <c r="E32">
-        <v>-20.56259344297865</v>
+        <v>-20.7950037860003</v>
       </c>
       <c r="F32">
-        <v>-0.3297657549953658</v>
+        <v>-0.8874392579080489</v>
       </c>
       <c r="G32">
-        <v>-4.753093734858166</v>
+        <v>-8.99130048187069</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.353796423840051</v>
       </c>
       <c r="E33">
-        <v>-19.31098662589467</v>
+        <v>-20.04977093245402</v>
       </c>
       <c r="F33">
-        <v>-0.1644070540485284</v>
+        <v>-0.5798962624750933</v>
       </c>
       <c r="G33">
-        <v>-4.829093928803214</v>
+        <v>-8.293603009469287</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.939977612596058</v>
       </c>
       <c r="E34">
-        <v>-20.31276658892349</v>
+        <v>-19.36228970792757</v>
       </c>
       <c r="F34">
-        <v>-0.1901311753750643</v>
+        <v>-0.3904701750073191</v>
       </c>
       <c r="G34">
-        <v>-3.884466175173113</v>
+        <v>-8.634635547651769</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.537013473903619</v>
       </c>
       <c r="E35">
-        <v>-18.64609795819247</v>
+        <v>-19.23271195267209</v>
       </c>
       <c r="F35">
-        <v>0.265457642286219</v>
+        <v>-0.7379752706861286</v>
       </c>
       <c r="G35">
-        <v>-5.311486761512576</v>
+        <v>-8.671137622767773</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.145443489513608</v>
       </c>
       <c r="E36">
-        <v>-18.14911152127268</v>
+        <v>-19.14441123799652</v>
       </c>
       <c r="F36">
-        <v>-0.07523164640235605</v>
+        <v>-0.548054647878883</v>
       </c>
       <c r="G36">
-        <v>-4.202854581866981</v>
+        <v>-8.612428408174338</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.774599943936511</v>
       </c>
       <c r="E37">
-        <v>-19.04455838612739</v>
+        <v>-18.6267477887577</v>
       </c>
       <c r="F37">
-        <v>0.4487910875064028</v>
+        <v>-0.2798292828524032</v>
       </c>
       <c r="G37">
-        <v>-4.322544045293791</v>
+        <v>-7.50271699068294</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.433268586341905</v>
       </c>
       <c r="E38">
-        <v>-17.01249624466547</v>
+        <v>-18.83833167981808</v>
       </c>
       <c r="F38">
-        <v>0.2066493552592737</v>
+        <v>-0.4367792262934227</v>
       </c>
       <c r="G38">
-        <v>-5.267608790935076</v>
+        <v>-7.528870300443182</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.132226530390322</v>
       </c>
       <c r="E39">
-        <v>-17.07474917684891</v>
+        <v>-18.69948866674291</v>
       </c>
       <c r="F39">
-        <v>-0.04301643810748328</v>
+        <v>-0.6041574869682852</v>
       </c>
       <c r="G39">
-        <v>-4.298436652676818</v>
+        <v>-7.672991589949813</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.885975056357427</v>
       </c>
       <c r="E40">
-        <v>-17.80167793845619</v>
+        <v>-17.29603758770773</v>
       </c>
       <c r="F40">
-        <v>-0.1676327167150297</v>
+        <v>-0.6459469657047147</v>
       </c>
       <c r="G40">
-        <v>-3.454154844887566</v>
+        <v>-7.778637719199035</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.703117790635464</v>
       </c>
       <c r="E41">
-        <v>-16.75389320798345</v>
+        <v>-16.63362599528774</v>
       </c>
       <c r="F41">
-        <v>0.09458781300855659</v>
+        <v>-0.6064528930414426</v>
       </c>
       <c r="G41">
-        <v>-4.041657498468788</v>
+        <v>-7.705292582776482</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.60000283288506</v>
       </c>
       <c r="E42">
-        <v>-17.50455570186492</v>
+        <v>-15.50081463684698</v>
       </c>
       <c r="F42">
-        <v>0.08719214883636262</v>
+        <v>-0.338011324122832</v>
       </c>
       <c r="G42">
-        <v>-3.853264283465482</v>
+        <v>-7.396037971225464</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.580145265328004</v>
       </c>
       <c r="E43">
-        <v>-16.04150990488881</v>
+        <v>-16.94828248323671</v>
       </c>
       <c r="F43">
-        <v>-0.2610402534221047</v>
+        <v>-0.7814264544325737</v>
       </c>
       <c r="G43">
-        <v>-4.512506458882711</v>
+        <v>-7.289931676146284</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.654129487008735</v>
       </c>
       <c r="E44">
-        <v>-13.76305349266954</v>
+        <v>-15.39576762529104</v>
       </c>
       <c r="F44">
-        <v>-0.1871855008907092</v>
+        <v>-0.7570136387046695</v>
       </c>
       <c r="G44">
-        <v>-4.407346979827762</v>
+        <v>-7.175767513224517</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.814524596400717</v>
       </c>
       <c r="E45">
-        <v>-12.82516124094094</v>
+        <v>-15.08657247699533</v>
       </c>
       <c r="F45">
-        <v>0.4303102107499459</v>
+        <v>-0.6824075569389348</v>
       </c>
       <c r="G45">
-        <v>-4.88553210915671</v>
+        <v>-7.227031310900132</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.059670374217273</v>
       </c>
       <c r="E46">
-        <v>-13.97356866386412</v>
+        <v>-14.13012253878329</v>
       </c>
       <c r="F46">
-        <v>-0.2967702246070558</v>
+        <v>-1.0298107634272</v>
       </c>
       <c r="G46">
-        <v>-5.274080907464351</v>
+        <v>-6.42603488603685</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.370224602247914</v>
       </c>
       <c r="E47">
-        <v>-12.88985502061452</v>
+        <v>-14.81297566287391</v>
       </c>
       <c r="F47">
-        <v>-0.2962690623283621</v>
+        <v>-1.105530170982297</v>
       </c>
       <c r="G47">
-        <v>-2.845328967487898</v>
+        <v>-6.914343663624889</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.736254851556636</v>
       </c>
       <c r="E48">
-        <v>-13.66601735163318</v>
+        <v>-13.82825898990599</v>
       </c>
       <c r="F48">
-        <v>-0.3842060607073493</v>
+        <v>-0.9698609861191969</v>
       </c>
       <c r="G48">
-        <v>-3.216255731889999</v>
+        <v>-6.732862867707582</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.133341738675229</v>
       </c>
       <c r="E49">
-        <v>-11.68530810541825</v>
+        <v>-12.95135622611269</v>
       </c>
       <c r="F49">
-        <v>-0.1397871464699243</v>
+        <v>-0.9937958338556858</v>
       </c>
       <c r="G49">
-        <v>-4.70551457436776</v>
+        <v>-7.140930642514766</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.551023022912174</v>
       </c>
       <c r="E50">
-        <v>-11.41045237552269</v>
+        <v>-12.94229022114933</v>
       </c>
       <c r="F50">
-        <v>-0.2068815926270731</v>
+        <v>-0.9860845617030253</v>
       </c>
       <c r="G50">
-        <v>-4.078993831060688</v>
+        <v>-7.302068136093252</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.967584853566262</v>
       </c>
       <c r="E51">
-        <v>-10.97966770012103</v>
+        <v>-12.99166870172897</v>
       </c>
       <c r="F51">
-        <v>-0.3460705105846684</v>
+        <v>-1.26933402631408</v>
       </c>
       <c r="G51">
-        <v>-4.813686649863446</v>
+        <v>-6.346816841827629</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.376795120604064</v>
       </c>
       <c r="E52">
-        <v>-10.68136806028777</v>
+        <v>-11.59625566405741</v>
       </c>
       <c r="F52">
-        <v>-0.3375722893993483</v>
+        <v>-1.331120294154089</v>
       </c>
       <c r="G52">
-        <v>-4.109550166388162</v>
+        <v>-7.063394355439495</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.766282403147082</v>
       </c>
       <c r="E53">
-        <v>-9.17223598333559</v>
+        <v>-11.65517563937121</v>
       </c>
       <c r="F53">
-        <v>-0.5311128777568276</v>
+        <v>-1.200230789205142</v>
       </c>
       <c r="G53">
-        <v>-3.856935678468534</v>
+        <v>-6.7547654369954</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.133308515329588</v>
       </c>
       <c r="E54">
-        <v>-9.48394896317957</v>
+        <v>-11.1819184062516</v>
       </c>
       <c r="F54">
-        <v>-0.429456458452675</v>
+        <v>-1.120184818705223</v>
       </c>
       <c r="G54">
-        <v>-4.369553791951442</v>
+        <v>-6.563866139018867</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.474872038957052</v>
       </c>
       <c r="E55">
-        <v>-10.43016907860828</v>
+        <v>-11.25972664665139</v>
       </c>
       <c r="F55">
-        <v>-0.4765433467300074</v>
+        <v>-1.560551556972663</v>
       </c>
       <c r="G55">
-        <v>-3.85086744849505</v>
+        <v>-7.002374380059649</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.788461394785035</v>
       </c>
       <c r="E56">
-        <v>-9.438759321057027</v>
+        <v>-10.6001498789602</v>
       </c>
       <c r="F56">
-        <v>-0.3090052111464046</v>
+        <v>-1.558449160504358</v>
       </c>
       <c r="G56">
-        <v>-4.56547187696551</v>
+        <v>-6.982587249371425</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.076190223914349</v>
       </c>
       <c r="E57">
-        <v>-9.239270984071133</v>
+        <v>-10.21649303255636</v>
       </c>
       <c r="F57">
-        <v>-0.2408040661391156</v>
+        <v>-1.466917047597221</v>
       </c>
       <c r="G57">
-        <v>-4.277189571405776</v>
+        <v>-7.048635943425425</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.332589608354356</v>
       </c>
       <c r="E58">
-        <v>-7.966262598826904</v>
+        <v>-10.25702740339901</v>
       </c>
       <c r="F58">
-        <v>-0.1717960912815</v>
+        <v>-1.499850450430321</v>
       </c>
       <c r="G58">
-        <v>-4.176886662656937</v>
+        <v>-7.323818420286264</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.560429977784052</v>
       </c>
       <c r="E59">
-        <v>-7.879062303335203</v>
+        <v>-10.27199400999437</v>
       </c>
       <c r="F59">
-        <v>0.1685154618713985</v>
+        <v>-1.420218663631801</v>
       </c>
       <c r="G59">
-        <v>-5.133313200589001</v>
+        <v>-7.283830340717407</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.750209759780108</v>
       </c>
       <c r="E60">
-        <v>-7.219050802139272</v>
+        <v>-9.261238611482343</v>
       </c>
       <c r="F60">
-        <v>-0.6447897364430037</v>
+        <v>-1.315431843912469</v>
       </c>
       <c r="G60">
-        <v>-3.831583520728795</v>
+        <v>-8.071928880159687</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.904988198276823</v>
       </c>
       <c r="E61">
-        <v>-8.034968606471278</v>
+        <v>-9.733744117916675</v>
       </c>
       <c r="F61">
-        <v>-0.5352853643647287</v>
+        <v>-1.323737055492937</v>
       </c>
       <c r="G61">
-        <v>-5.357854262335608</v>
+        <v>-8.068565365891788</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.014644418507244</v>
       </c>
       <c r="E62">
-        <v>-6.641004680482173</v>
+        <v>-9.295976535595182</v>
       </c>
       <c r="F62">
-        <v>-0.1874903400949395</v>
+        <v>-1.10409295353844</v>
       </c>
       <c r="G62">
-        <v>-5.339980626969083</v>
+        <v>-8.307785386559525</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.084710715389928</v>
       </c>
       <c r="E63">
-        <v>-7.786314627184106</v>
+        <v>-10.07666734062152</v>
       </c>
       <c r="F63">
-        <v>-0.6244673989501235</v>
+        <v>-1.220358460358365</v>
       </c>
       <c r="G63">
-        <v>-5.883522546334323</v>
+        <v>-7.670478885885506</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.108013762125399</v>
       </c>
       <c r="E64">
-        <v>-6.963038052589636</v>
+        <v>-9.286367113750904</v>
       </c>
       <c r="F64">
-        <v>-0.1985324775742569</v>
+        <v>-1.097899250467708</v>
       </c>
       <c r="G64">
-        <v>-5.20713174502367</v>
+        <v>-8.775949494541099</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.092101679607826</v>
       </c>
       <c r="E65">
-        <v>-6.477350158318974</v>
+        <v>-9.341129949925662</v>
       </c>
       <c r="F65">
-        <v>-0.5602863209486205</v>
+        <v>-1.479831295406865</v>
       </c>
       <c r="G65">
-        <v>-6.779187331438604</v>
+        <v>-7.874818998751482</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.034384837430963</v>
       </c>
       <c r="E66">
-        <v>-7.47951051316444</v>
+        <v>-8.959202980592751</v>
       </c>
       <c r="F66">
-        <v>-0.6670984989677972</v>
+        <v>-1.469509837567983</v>
       </c>
       <c r="G66">
-        <v>-5.627130725954387</v>
+        <v>-7.753305424732533</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.940850701175286</v>
       </c>
       <c r="E67">
-        <v>-7.366162808752451</v>
+        <v>-9.635621143118474</v>
       </c>
       <c r="F67">
-        <v>-0.05212847953827784</v>
+        <v>-1.388793717839199</v>
       </c>
       <c r="G67">
-        <v>-6.12105418877703</v>
+        <v>-8.346055292993499</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.814453331047385</v>
       </c>
       <c r="E68">
-        <v>-7.416279430595338</v>
+        <v>-8.434742291868417</v>
       </c>
       <c r="F68">
-        <v>-0.4541476056279199</v>
+        <v>-1.126602180974711</v>
       </c>
       <c r="G68">
-        <v>-6.471472123563347</v>
+        <v>-8.422691111682088</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.657057714930742</v>
       </c>
       <c r="E69">
-        <v>-6.298837712936609</v>
+        <v>-9.700509647174382</v>
       </c>
       <c r="F69">
-        <v>-0.524442863429486</v>
+        <v>-1.479753428871002</v>
       </c>
       <c r="G69">
-        <v>-5.85360183575039</v>
+        <v>-7.826028178593702</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.476300191110427</v>
       </c>
       <c r="E70">
-        <v>-6.997671821800298</v>
+        <v>-8.94212157663582</v>
       </c>
       <c r="F70">
-        <v>-0.735250770298321</v>
+        <v>-1.607046162556993</v>
       </c>
       <c r="G70">
-        <v>-5.399199665575567</v>
+        <v>-8.091103559923146</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.269115249841158</v>
       </c>
       <c r="E71">
-        <v>-7.360497687768855</v>
+        <v>-7.295215206474279</v>
       </c>
       <c r="F71">
-        <v>-0.6444169711117439</v>
+        <v>-1.100097737554738</v>
       </c>
       <c r="G71">
-        <v>-4.649642497301481</v>
+        <v>-8.028252852860083</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.046800621415465</v>
       </c>
       <c r="E72">
-        <v>-7.085655543295326</v>
+        <v>-8.835068451094493</v>
       </c>
       <c r="F72">
-        <v>-0.2671784558768491</v>
+        <v>-1.393450799377738</v>
       </c>
       <c r="G72">
-        <v>-6.093920957537164</v>
+        <v>-8.448235281063104</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.806932496887843</v>
       </c>
       <c r="E73">
-        <v>-6.719138971010518</v>
+        <v>-9.522495333932861</v>
       </c>
       <c r="F73">
-        <v>-0.7446237474609974</v>
+        <v>-1.560347778591574</v>
       </c>
       <c r="G73">
-        <v>-5.238711038922777</v>
+        <v>-8.340920636862089</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.563927541479582</v>
       </c>
       <c r="E74">
-        <v>-8.351862160580035</v>
+        <v>-9.699558667632772</v>
       </c>
       <c r="F74">
-        <v>-0.442599335665492</v>
+        <v>-2.080737293071654</v>
       </c>
       <c r="G74">
-        <v>-5.373000008177774</v>
+        <v>-7.866320828352173</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.317455451159895</v>
       </c>
       <c r="E75">
-        <v>-8.0812088545636</v>
+        <v>-9.857606938974474</v>
       </c>
       <c r="F75">
-        <v>-0.5578658313976405</v>
+        <v>-1.945234610056517</v>
       </c>
       <c r="G75">
-        <v>-5.976641571262943</v>
+        <v>-7.584073647310529</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.082106390584054</v>
       </c>
       <c r="E76">
-        <v>-7.057130685521011</v>
+        <v>-10.21240382052743</v>
       </c>
       <c r="F76">
-        <v>-0.8840620040068353</v>
+        <v>-1.594546098448749</v>
       </c>
       <c r="G76">
-        <v>-6.415093533029558</v>
+        <v>-7.798054068786861</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.857638678862401</v>
       </c>
       <c r="E77">
-        <v>-6.700359389300709</v>
+        <v>-9.892358448509336</v>
       </c>
       <c r="F77">
-        <v>-0.9597474484984178</v>
+        <v>-1.783835505295061</v>
       </c>
       <c r="G77">
-        <v>-4.978316768985863</v>
+        <v>-8.069882963016418</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.654780854444352</v>
       </c>
       <c r="E78">
-        <v>-7.35397668519781</v>
+        <v>-10.81480860387179</v>
       </c>
       <c r="F78">
-        <v>-0.5756765589252326</v>
+        <v>-1.812767065205237</v>
       </c>
       <c r="G78">
-        <v>-6.082065893961034</v>
+        <v>-7.366785990840464</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.471328454381936</v>
       </c>
       <c r="E79">
-        <v>-8.696637529154017</v>
+        <v>-11.63764138801351</v>
       </c>
       <c r="F79">
-        <v>-1.33480735746395</v>
+        <v>-2.045694866831027</v>
       </c>
       <c r="G79">
-        <v>-5.351173581437359</v>
+        <v>-7.396061145044239</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.312674367445958</v>
       </c>
       <c r="E80">
-        <v>-10.488450539087</v>
+        <v>-10.84095601279208</v>
       </c>
       <c r="F80">
-        <v>-1.298931593616106</v>
+        <v>-2.111667703524785</v>
       </c>
       <c r="G80">
-        <v>-6.435023017175971</v>
+        <v>-7.667413320716141</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.176157699092895</v>
       </c>
       <c r="E81">
-        <v>-10.38012038387551</v>
+        <v>-11.85940528864313</v>
       </c>
       <c r="F81">
-        <v>-1.536611739031757</v>
+        <v>-1.673501109079181</v>
       </c>
       <c r="G81">
-        <v>-5.688329470793355</v>
+        <v>-7.990810582810926</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.060740637501997</v>
       </c>
       <c r="E82">
-        <v>-12.34189155179037</v>
+        <v>-12.35977449564666</v>
       </c>
       <c r="F82">
-        <v>-1.426766079583529</v>
+        <v>-2.42550711958642</v>
       </c>
       <c r="G82">
-        <v>-5.110599547644061</v>
+        <v>-7.776015767131933</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.964945483104338</v>
       </c>
       <c r="E83">
-        <v>-12.28177605933855</v>
+        <v>-13.02705872609891</v>
       </c>
       <c r="F83">
-        <v>-1.909753977459808</v>
+        <v>-2.371648327791202</v>
       </c>
       <c r="G83">
-        <v>-4.151782795832644</v>
+        <v>-7.539801721813856</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.882497942082775</v>
       </c>
       <c r="E84">
-        <v>-12.3501152605883</v>
+        <v>-14.08371926562669</v>
       </c>
       <c r="F84">
-        <v>-1.752339319905818</v>
+        <v>-2.173003339497672</v>
       </c>
       <c r="G84">
-        <v>-4.170447651583054</v>
+        <v>-7.573844061594181</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.81496842531812</v>
       </c>
       <c r="E85">
-        <v>-13.36258242227522</v>
+        <v>-15.13545282543412</v>
       </c>
       <c r="F85">
-        <v>-1.959772457975648</v>
+        <v>-3.105750833621735</v>
       </c>
       <c r="G85">
-        <v>-4.291669897594548</v>
+        <v>-7.686637658662689</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.754770223338389</v>
       </c>
       <c r="E86">
-        <v>-14.10195090198157</v>
+        <v>-15.77895351039809</v>
       </c>
       <c r="F86">
-        <v>-2.049473050555195</v>
+        <v>-2.535346980462829</v>
       </c>
       <c r="G86">
-        <v>-4.516485734620915</v>
+        <v>-7.017407567353479</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.707652556974042</v>
       </c>
       <c r="E87">
-        <v>-14.9186476038429</v>
+        <v>-17.50894832165237</v>
       </c>
       <c r="F87">
-        <v>-2.122423225882734</v>
+        <v>-2.84354272940919</v>
       </c>
       <c r="G87">
-        <v>-4.898622006218988</v>
+        <v>-7.773516305249784</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.6684030234429</v>
       </c>
       <c r="E88">
-        <v>-17.44339413191733</v>
+        <v>-18.53769081892285</v>
       </c>
       <c r="F88">
-        <v>-2.122817528766467</v>
+        <v>-2.710053807550258</v>
       </c>
       <c r="G88">
-        <v>-4.941314801493429</v>
+        <v>-7.684770510978541</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.646633620112041</v>
       </c>
       <c r="E89">
-        <v>-18.24815377629443</v>
+        <v>-19.77454839616385</v>
       </c>
       <c r="F89">
-        <v>-2.186887605535994</v>
+        <v>-2.795964619261998</v>
       </c>
       <c r="G89">
-        <v>-5.281963316393356</v>
+        <v>-7.679711997394534</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.640473390876372</v>
       </c>
       <c r="E90">
-        <v>-19.47474983143405</v>
+        <v>-21.36461336058111</v>
       </c>
       <c r="F90">
-        <v>-2.687009454771779</v>
+        <v>-2.960066686858788</v>
       </c>
       <c r="G90">
-        <v>-4.590916729980349</v>
+        <v>-7.556771578248159</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.663552816405095</v>
       </c>
       <c r="E91">
-        <v>-22.42685750856035</v>
+        <v>-23.79759941983812</v>
       </c>
       <c r="F91">
-        <v>-2.317681019866217</v>
+        <v>-3.085263651015697</v>
       </c>
       <c r="G91">
-        <v>-4.555474029436912</v>
+        <v>-7.813971171739677</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.716396451894803</v>
       </c>
       <c r="E92">
-        <v>-25.53498922914692</v>
+        <v>-25.78895057997108</v>
       </c>
       <c r="F92">
-        <v>-2.620360670277336</v>
+        <v>-3.726185592807522</v>
       </c>
       <c r="G92">
-        <v>-4.621910057319006</v>
+        <v>-7.725844449484278</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.814860461648857</v>
       </c>
       <c r="E93">
-        <v>-25.62017435370521</v>
+        <v>-27.00956452094657</v>
       </c>
       <c r="F93">
-        <v>-2.795322634524828</v>
+        <v>-3.741708369568582</v>
       </c>
       <c r="G93">
-        <v>-4.976492658393725</v>
+        <v>-7.67559698928922</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.959627680614473</v>
       </c>
       <c r="E94">
-        <v>-28.11621488504502</v>
+        <v>-29.17156216711057</v>
       </c>
       <c r="F94">
-        <v>-2.916455628203603</v>
+        <v>-3.231026492681909</v>
       </c>
       <c r="G94">
-        <v>-5.292434571934071</v>
+        <v>-8.307646343646875</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.16142763499902</v>
       </c>
       <c r="E95">
-        <v>-30.09910232725765</v>
+        <v>-32.31639264105531</v>
       </c>
       <c r="F95">
-        <v>-2.607917763519885</v>
+        <v>-3.486161996009352</v>
       </c>
       <c r="G95">
-        <v>-6.748882597572115</v>
+        <v>-8.050102453419273</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.42342331384457</v>
       </c>
       <c r="E96">
-        <v>-33.47174900734326</v>
+        <v>-33.02577356588286</v>
       </c>
       <c r="F96">
-        <v>-2.562045261855057</v>
+        <v>-3.438771096895192</v>
       </c>
       <c r="G96">
-        <v>-5.811829372135866</v>
+        <v>-8.146277111880639</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.74102657924865</v>
       </c>
       <c r="E97">
-        <v>-35.87273234078805</v>
+        <v>-35.58673656483364</v>
       </c>
       <c r="F97">
-        <v>-3.12700674117757</v>
+        <v>-3.869923904541293</v>
       </c>
       <c r="G97">
-        <v>-6.133111195631057</v>
+        <v>-8.953431151446965</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.122509295312321</v>
       </c>
       <c r="E98">
-        <v>-38.28199598895588</v>
+        <v>-37.51770958102233</v>
       </c>
       <c r="F98">
-        <v>-3.019328919222468</v>
+        <v>-3.784583837970082</v>
       </c>
       <c r="G98">
-        <v>-5.589936746820675</v>
+        <v>-9.154917574058089</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.53932955895533</v>
       </c>
       <c r="E99">
-        <v>-42.42981100001548</v>
+        <v>-40.91556174743463</v>
       </c>
       <c r="F99">
-        <v>-3.498453311532091</v>
+        <v>-3.856907767541104</v>
       </c>
       <c r="G99">
-        <v>-6.580557909627871</v>
+        <v>-9.1359680113913</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.013346714590493</v>
       </c>
       <c r="E100">
-        <v>-42.65710190317147</v>
+        <v>-43.37458653223575</v>
       </c>
       <c r="F100">
-        <v>-3.378252231181465</v>
+        <v>-4.08285988726792</v>
       </c>
       <c r="G100">
-        <v>-6.383686387498493</v>
+        <v>-8.713999255864717</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.479148371734277</v>
       </c>
       <c r="E101">
-        <v>-45.85962060749991</v>
+        <v>-44.80341970808391</v>
       </c>
       <c r="F101">
-        <v>-3.500810845160458</v>
+        <v>-4.142110522487959</v>
       </c>
       <c r="G101">
-        <v>-7.805201536606147</v>
+        <v>-8.759039227926502</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.005806730258147</v>
       </c>
       <c r="E102">
-        <v>-48.3835157824609</v>
+        <v>-48.55091535262844</v>
       </c>
       <c r="F102">
-        <v>-3.50346576268643</v>
+        <v>-4.146782514639749</v>
       </c>
       <c r="G102">
-        <v>-6.370103219150863</v>
+        <v>-9.448417299387716</v>
       </c>
     </row>
   </sheetData>
